--- a/voice-assist/docs/Charlie-Voice-Settings-Tracker.xlsx
+++ b/voice-assist/docs/Charlie-Voice-Settings-Tracker.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -206,6 +206,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -688,14 +697,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
@@ -710,7 +719,7 @@
     <row r="2">
       <c r="A2" s="22" t="inlineStr">
         <is>
-          <t>Yellow = confirm first (read at step 0).   Orange = the fix.   Green = leave alone for now.   Grey = watch only, don't touch yet.</t>
+          <t>READ FROM THE LIVE API 13 Aug — no longer presumed.   Orange = changed today.   Green = read, left alone.   Grey = watch only.</t>
         </is>
       </c>
     </row>
@@ -752,83 +761,83 @@
       </c>
     </row>
     <row r="5" ht="46" customHeight="1">
-      <c r="A5" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>transcriber.endpointing (Deepgram)</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>Deepgram's OWN silence timer, upstream of everything. If low, it finalises early and nothing downstream can rescue it. CONFIRM FIRST — and if the field isn't in the JSON at all, that closes this row.</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>Deepgram's own silence timer. FIELD IS ABSENT from the live config — never set, so it runs on Deepgram's default and isn't reachable from Vapi. Not the upstream danger we feared.</t>
+        </is>
+      </c>
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F5" s="10" t="inlineStr">
-        <is>
-          <t>Read value first — don't change yet</t>
-        </is>
-      </c>
-      <c r="G5" s="10" t="inlineStr">
-        <is>
-          <t>Needs read</t>
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>ABSENT</t>
+        </is>
+      </c>
+      <c r="F5" s="19" t="inlineStr">
+        <is>
+          <t>Nothing to do — closed</t>
+        </is>
+      </c>
+      <c r="G5" s="19" t="inlineStr">
+        <is>
+          <t>Closed 13 Aug</t>
         </is>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>transcriptionEndpointingPlan.waitSeconds</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>Base delay applied BEFORE the punctuation branches. Never needs changing, but if it's set to anything it ADDS to setting #1 and will confound the test. Read it at step 0.</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>Base delay before the punctuation branches. ABSENT — never set, so it adds nothing and cannot confound the test.</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>not stated</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>Read value only — never change</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>Needs read</t>
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>ABSENT</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="inlineStr">
+        <is>
+          <t>Nothing to do — closed</t>
+        </is>
+      </c>
+      <c r="G6" s="19" t="inlineStr">
+        <is>
+          <t>Closed 13 Aug</t>
         </is>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
@@ -838,7 +847,7 @@
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>Silence to wait when your sentence ends with punctuation, before Charlie talks. THE cut-off culprit.</t>
+          <t>Silence to wait when your sentence ends with punctuation. THE culprit — Deepgram drops a comma after a filler word and this fired at 100ms, splitting one sentence into three or four turns.</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
@@ -848,91 +857,91 @@
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>presumed</t>
+          <t>0.1s  -&gt;  1s</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>0.6s (then try 0.35 if short answers drag)</t>
+          <t>Changed to 1.0s</t>
         </is>
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
-          <t>Not changed</t>
+          <t>CHANGED 13 Aug</t>
         </is>
       </c>
     </row>
     <row r="8" ht="46" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>smartEndpointingPlan.provider</t>
+          <t>onNoPunctuationSeconds</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>Whether your actual words get a vote on 'are you finished', or only silence decides. Off = silence only.</t>
+          <t>Silence to wait when there is NO punctuation. Was set BELOW Vapi's own default of 1.5s.</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>off</t>
+          <t>1.5s</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>presumed</t>
+          <t>1s  -&gt;  2s</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>livekit (conservative) — only if #1 not enough</t>
+          <t>Changed to 2.0s</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
-          <t>Not changed</t>
+          <t>CHANGED 13 Aug</t>
         </is>
       </c>
     </row>
     <row r="9" ht="46" customHeight="1">
-      <c r="A9" s="25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>transcriber.smartFormat</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>Inserts the punctuation that triggers setting #1. Coupled to it — don't move both at once.</t>
-        </is>
-      </c>
-      <c r="D9" s="19" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="E9" s="19" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F9" s="19" t="inlineStr">
-        <is>
-          <t>Leave on for now</t>
-        </is>
-      </c>
-      <c r="G9" s="19" t="inlineStr">
-        <is>
-          <t>Not changed</t>
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>onNumberSeconds</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Silence after a number. Was BELOW default. Matters most of all — job numbers get read aloud with pauses between the digits.</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>0.4s  -&gt;  2s</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>Changed to 2.0s</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>CHANGED 13 Aug</t>
         </is>
       </c>
     </row>
@@ -944,22 +953,22 @@
       </c>
       <c r="B10" s="18" t="inlineStr">
         <is>
-          <t>onNoPunctuationSeconds</t>
+          <t>smartEndpointingPlan (livekit + waitFunction)</t>
         </is>
       </c>
       <c r="C10" s="19" t="inlineStr">
         <is>
-          <t>Silence to wait when there's NO punctuation. Already generous.</t>
+          <t>Was already ON with a conservative 2-second-floor wait function, PUBLISHED and live during a test that still fragmented. A red herring — it was never the thing cutting you off.</t>
         </is>
       </c>
       <c r="D10" s="19" t="inlineStr">
         <is>
-          <t>1.5s</t>
+          <t>off</t>
         </is>
       </c>
       <c r="E10" s="19" t="inlineStr">
         <is>
-          <t>presumed</t>
+          <t>livekit, 2000 + 4000 * max(0, x-0.5)</t>
         </is>
       </c>
       <c r="F10" s="19" t="inlineStr">
@@ -969,7 +978,7 @@
       </c>
       <c r="G10" s="19" t="inlineStr">
         <is>
-          <t>Not changed</t>
+          <t>Read, unchanged</t>
         </is>
       </c>
     </row>
@@ -981,22 +990,22 @@
       </c>
       <c r="B11" s="18" t="inlineStr">
         <is>
-          <t>onNumberSeconds</t>
+          <t>startSpeakingPlan.waitSeconds</t>
         </is>
       </c>
       <c r="C11" s="19" t="inlineStr">
         <is>
-          <t>Silence to wait when you end on a number (job numbers etc).</t>
+          <t>Final pause after the turn commits, before Charlie speaks. Set below default.</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
         <is>
-          <t>0.5s</t>
+          <t>0.4s</t>
         </is>
       </c>
       <c r="E11" s="19" t="inlineStr">
         <is>
-          <t>presumed</t>
+          <t>0.2s</t>
         </is>
       </c>
       <c r="F11" s="19" t="inlineStr">
@@ -1006,7 +1015,7 @@
       </c>
       <c r="G11" s="19" t="inlineStr">
         <is>
-          <t>Not changed</t>
+          <t>Read, unchanged</t>
         </is>
       </c>
     </row>
@@ -1018,22 +1027,22 @@
       </c>
       <c r="B12" s="18" t="inlineStr">
         <is>
-          <t>startSpeakingPlan.waitSeconds</t>
+          <t>stopSpeakingPlan.numWords</t>
         </is>
       </c>
       <c r="C12" s="19" t="inlineStr">
         <is>
-          <t>Final pause after the turn commits, before Charlie's audio starts. Affects wait, not cut-off.</t>
+          <t>Words needed to cut Charlie off. Already raised off 0 before we started — the van road-noise protection is in place.</t>
         </is>
       </c>
       <c r="D12" s="19" t="inlineStr">
         <is>
-          <t>0.4s</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E12" s="19" t="inlineStr">
         <is>
-          <t>presumed</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F12" s="19" t="inlineStr">
@@ -1043,44 +1052,155 @@
       </c>
       <c r="G12" s="19" t="inlineStr">
         <is>
-          <t>Not changed</t>
+          <t>Read, unchanged</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B13" s="31" t="inlineStr">
+        <is>
+          <t>stopSpeakingPlan.backoffSeconds</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="inlineStr">
+        <is>
+          <t>How long Charlie stays quiet after being interrupted.</t>
+        </is>
+      </c>
+      <c r="D13" s="32" t="inlineStr">
+        <is>
+          <t>1.0s</t>
+        </is>
+      </c>
+      <c r="E13" s="32" t="inlineStr">
+        <is>
+          <t>0.8s</t>
+        </is>
+      </c>
+      <c r="F13" s="32" t="inlineStr">
+        <is>
+          <t>Leave as is</t>
+        </is>
+      </c>
+      <c r="G13" s="32" t="inlineStr">
+        <is>
+          <t>Read, unchanged</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="26" t="inlineStr">
         <is>
           <t>watch</t>
         </is>
       </c>
-      <c r="B13" s="27" t="inlineStr">
-        <is>
-          <t>stopSpeakingPlan.numWords</t>
-        </is>
-      </c>
-      <c r="C13" s="28" t="inlineStr">
-        <is>
-          <t>Words needed to cut Charlie off. 0 = any noise interrupts. Watch for van road-noise phantom triggers.</t>
-        </is>
-      </c>
-      <c r="D13" s="28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E13" s="28" t="inlineStr">
-        <is>
-          <t>presumed</t>
-        </is>
-      </c>
-      <c r="F13" s="28" t="inlineStr">
-        <is>
-          <t>Bump to 2 ONLY if road noise cuts Charlie off</t>
-        </is>
-      </c>
-      <c r="G13" s="28" t="inlineStr">
-        <is>
-          <t>Not changed</t>
+      <c r="B14" s="27" t="inlineStr">
+        <is>
+          <t>backgroundSound</t>
+        </is>
+      </c>
+      <c r="C14" s="28" t="inlineStr">
+        <is>
+          <t>A CUSTOM AMBIENT WAV plays through every call. The sound spec says kill any noise while the user talks. Left on deliberately — someone chose it. One field to switch off when that call is made.</t>
+        </is>
+      </c>
+      <c r="D14" s="28" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="E14" s="28" t="inlineStr">
+        <is>
+          <t>ai-ambient.wav</t>
+        </is>
+      </c>
+      <c r="F14" s="28" t="inlineStr">
+        <is>
+          <t>Your decision</t>
+        </is>
+      </c>
+      <c r="G14" s="28" t="inlineStr">
+        <is>
+          <t>Flagged, not changed</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B15" s="31" t="inlineStr">
+        <is>
+          <t>transcriber model / language</t>
+        </is>
+      </c>
+      <c r="C15" s="32" t="inlineStr">
+        <is>
+          <t>The ears. Flux models have purpose-built end-of-turn detection that nova-2 cannot do — the fallback if timers aren't enough.</t>
+        </is>
+      </c>
+      <c r="D15" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" s="32" t="inlineStr">
+        <is>
+          <t>deepgram nova-2, en-AU</t>
+        </is>
+      </c>
+      <c r="F15" s="32" t="inlineStr">
+        <is>
+          <t>Leave as is</t>
+        </is>
+      </c>
+      <c r="G15" s="32" t="inlineStr">
+        <is>
+          <t>Read, unchanged</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B16" s="31" t="inlineStr">
+        <is>
+          <t>silenceTimeoutSeconds</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="inlineStr">
+        <is>
+          <t>Hangs up after total silence.</t>
+        </is>
+      </c>
+      <c r="D16" s="32" t="inlineStr">
+        <is>
+          <t>30s</t>
+        </is>
+      </c>
+      <c r="E16" s="32" t="inlineStr">
+        <is>
+          <t>120s</t>
+        </is>
+      </c>
+      <c r="F16" s="32" t="inlineStr">
+        <is>
+          <t>Leave as is</t>
+        </is>
+      </c>
+      <c r="G16" s="32" t="inlineStr">
+        <is>
+          <t>Read, unchanged</t>
         </is>
       </c>
     </row>
@@ -1140,52 +1260,112 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
-        <is>
-          <t>10/08/26</t>
-        </is>
-      </c>
-      <c r="B4" s="20" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>13/08/26</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>LIVE READ (no change)</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>presumed defaults</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>real values</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>Every presumed value was WRONG — assistant was tuned tighter than default. Deepgram endpointing confirmed ABSENT, priority 0 closed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>13/08/26</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>onPunctuationSeconds</t>
         </is>
       </c>
-      <c r="C4" s="20" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-      <c r="E4" s="20" t="inlineStr">
-        <is>
-          <t>EXAMPLE ROW — delete me.  e.g. '(1) n — no cut-off on test sentence.  (2) y — 'yeah' felt slow. Try 0.35 next.'</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="21" t="n"/>
-      <c r="B5" s="21" t="n"/>
-      <c r="C5" s="21" t="n"/>
-      <c r="D5" s="21" t="n"/>
-      <c r="E5" s="21" t="n"/>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>PENDING TEST</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="n"/>
-      <c r="B6" s="21" t="n"/>
-      <c r="C6" s="21" t="n"/>
-      <c r="D6" s="21" t="n"/>
-      <c r="E6" s="21" t="n"/>
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>13/08/26</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>onNoPunctuationSeconds</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>same edit — one plan</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="n"/>
-      <c r="B7" s="21" t="n"/>
-      <c r="C7" s="21" t="n"/>
-      <c r="D7" s="21" t="n"/>
-      <c r="E7" s="21" t="n"/>
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>13/08/26</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>onNumberSeconds</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>same edit — job numbers read aloud with pauses</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="21" t="n"/>

--- a/voice-assist/docs/Charlie-Voice-Settings-Tracker.xlsx
+++ b/voice-assist/docs/Charlie-Voice-Settings-Tracker.xlsx
@@ -1368,32 +1368,112 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="n"/>
-      <c r="B8" s="21" t="n"/>
-      <c r="C8" s="21" t="n"/>
-      <c r="D8" s="21" t="n"/>
-      <c r="E8" s="21" t="n"/>
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>13/08/26</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>onPunctuationSeconds</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>Raised to the CAP. Vapi rejects anything over 3s (400: "must not be greater than 3").</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="n"/>
-      <c r="B9" s="21" t="n"/>
-      <c r="C9" s="21" t="n"/>
-      <c r="D9" s="21" t="n"/>
-      <c r="E9" s="21" t="n"/>
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>13/08/26</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>onNoPunctuationSeconds</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>same edit</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="n"/>
-      <c r="B10" s="21" t="n"/>
-      <c r="C10" s="21" t="n"/>
-      <c r="D10" s="21" t="n"/>
-      <c r="E10" s="21" t="n"/>
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>13/08/26</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>onNumberSeconds</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>same edit</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="n"/>
-      <c r="B11" s="21" t="n"/>
-      <c r="C11" s="21" t="n"/>
-      <c r="D11" s="21" t="n"/>
-      <c r="E11" s="21" t="n"/>
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>13/08/26</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>(rationale)</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>Deliberate: park the dumb timers at their ceiling so LiveKit smart endpointing becomes the governing constraint. Its curve floors at 2s and rises to 6s when it judges you are still speaking — which no fixed silence timer can do. Turn was still splitting after a &gt;2s thinking pause mid-sentence, so bigger fixed timers were the wrong tool.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="21" t="n"/>

--- a/voice-assist/docs/Charlie-Voice-Settings-Tracker.xlsx
+++ b/voice-assist/docs/Charlie-Voice-Settings-Tracker.xlsx
@@ -1476,25 +1476,85 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="21" t="n"/>
-      <c r="B12" s="21" t="n"/>
-      <c r="C12" s="21" t="n"/>
-      <c r="D12" s="21" t="n"/>
-      <c r="E12" s="21" t="n"/>
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>13/08/26</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>stopSpeakingPlan.backoffSeconds</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>The ping-pong. Charlie was interrupted correctly at 2 words, then barged back in 0.8s later while Steven was still mid-sentence, got cut off again, and cycled. Now stays down 3s once interrupted.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="n"/>
-      <c r="B13" s="21" t="n"/>
-      <c r="C13" s="21" t="n"/>
-      <c r="D13" s="21" t="n"/>
-      <c r="E13" s="21" t="n"/>
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>13/08/26</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>(app) speaking-label debounce</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>instant</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>350ms</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="inlineStr">
+        <is>
+          <t>UI only. Empty speech turns for held-back fragments were rendering as SPEAKING. Label was lying; mic never stopped.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="21" t="n"/>
-      <c r="B14" s="21" t="n"/>
-      <c r="C14" s="21" t="n"/>
-      <c r="D14" s="21" t="n"/>
-      <c r="E14" s="21" t="n"/>
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>13/08/26</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>(observed)</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>Fragments still split into bubbles but Charlie now answers the whole thought once — the goal. Remaining: "Voice error - Meeting has ended" seen twice on a phone in the red battery zone; not chased, suspect iOS power management. Deepgram keywords still empty (Marites -&gt; "many tiers"). backgroundSound ambient WAV still on.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
